--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92551214717</v>
+        <v>46157.93104344438</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93104344438</v>
+        <v>46157.93129862747</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93129862747</v>
+        <v>46157.93378188709</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93378188709</v>
+        <v>46157.9368798483</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9368798483</v>
+        <v>46158.28201957141</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28201957141</v>
+        <v>46158.29731325565</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29731325565</v>
+        <v>46158.29801050812</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29801050812</v>
+        <v>46158.33365224742</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33365224742</v>
+        <v>46158.37216839745</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37216839745</v>
+        <v>46158.37272510278</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
